--- a/ip_cimzes.xlsx
+++ b/ip_cimzes.xlsx
@@ -8,20 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vizsgaremek\NL_EZS_vizsga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A0D00B-50E3-45D9-BFCE-1DB4992D835A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEDCD50-AABE-4318-A561-183480B29DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hálózatok" sheetId="1" r:id="rId1"/>
     <sheet name="VLAN-ok - Bal oldal" sheetId="2" r:id="rId2"/>
+    <sheet name="routerek" sheetId="4" r:id="rId3"/>
+    <sheet name="vlan - telephely" sheetId="5" r:id="rId4"/>
+    <sheet name="vlan jobb oldal" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="83">
   <si>
     <t>Hálózat</t>
   </si>
@@ -77,15 +80,9 @@
     <t>10.10.30.1 – 10.10.30.254</t>
   </si>
   <si>
-    <t>10.10.40.1 – 10.10.40.2</t>
-  </si>
-  <si>
     <t>255.255.255.0</t>
   </si>
   <si>
-    <t>255.255.255.252</t>
-  </si>
-  <si>
     <t>10.10.10.255</t>
   </si>
   <si>
@@ -95,15 +92,9 @@
     <t>10.10.30.255</t>
   </si>
   <si>
-    <t>10.10.40.3</t>
-  </si>
-  <si>
     <t>0.0.0.255</t>
   </si>
   <si>
-    <t>0.0.0.3</t>
-  </si>
-  <si>
     <t>10.10.10.1</t>
   </si>
   <si>
@@ -171,6 +162,117 @@
   </si>
   <si>
     <t>đ</t>
+  </si>
+  <si>
+    <t>10.10.40.1 - 10.10.40.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.255.255.248	</t>
+  </si>
+  <si>
+    <t>10.10.40.7</t>
+  </si>
+  <si>
+    <t>0.0.0.7</t>
+  </si>
+  <si>
+    <t>s0/0/0</t>
+  </si>
+  <si>
+    <t>255.255.255.248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S0/0/0 </t>
+  </si>
+  <si>
+    <t>Router1-telephely -- Router-Iroda3</t>
+  </si>
+  <si>
+    <t>Eszkoz irányok</t>
+  </si>
+  <si>
+    <t>Port</t>
+  </si>
+  <si>
+    <t>ip</t>
+  </si>
+  <si>
+    <t>mask</t>
+  </si>
+  <si>
+    <t>s0/0/1</t>
+  </si>
+  <si>
+    <t>Router1-telephely -- Router-Iroda2</t>
+  </si>
+  <si>
+    <t>10.10.40.1</t>
+  </si>
+  <si>
+    <t>10.10.40.2</t>
+  </si>
+  <si>
+    <t>10.10.41.1</t>
+  </si>
+  <si>
+    <t>10.10.41.2</t>
+  </si>
+  <si>
+    <t>Teljes hálózat</t>
+  </si>
+  <si>
+    <t>VLAN 10 - Menedzsment</t>
+  </si>
+  <si>
+    <t>10.10.20.1 – 10.10.20.126</t>
+  </si>
+  <si>
+    <t>255.255.255.128</t>
+  </si>
+  <si>
+    <t>10.10.20.127</t>
+  </si>
+  <si>
+    <t>0.0.0.127</t>
+  </si>
+  <si>
+    <t>VLAN 20 - Felhasználói</t>
+  </si>
+  <si>
+    <t>10.10.20.129 – 10.10.20.254</t>
+  </si>
+  <si>
+    <t>10.10.20.129</t>
+  </si>
+  <si>
+    <t>IP-tartomány</t>
+  </si>
+  <si>
+    <t>Subnet Mask</t>
+  </si>
+  <si>
+    <t>Wildcard Mask</t>
+  </si>
+  <si>
+    <t>Gateway</t>
+  </si>
+  <si>
+    <t>VLAN 30 - Menedzsment</t>
+  </si>
+  <si>
+    <t>10.10.30.1 – 10.10.30.126</t>
+  </si>
+  <si>
+    <t>10.10.30.127</t>
+  </si>
+  <si>
+    <t>VLAN 40 - Felhasználói</t>
+  </si>
+  <si>
+    <t>10.10.30.129 – 10.10.30.254</t>
+  </si>
+  <si>
+    <t>10.10.30.129</t>
   </si>
 </sst>
 </file>
@@ -202,7 +304,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -225,11 +327,96 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -542,7 +729,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -579,16 +771,16 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -602,16 +794,16 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -625,16 +817,16 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
         <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -645,28 +837,30 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-    </row>
+    </row>
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -674,16 +868,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="35" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -691,58 +888,358 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>42</v>
-      </c>
-      <c r="D2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>43</v>
-      </c>
-      <c r="D3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>44</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>41</v>
       </c>
-      <c r="C5" t="s">
-        <v>45</v>
-      </c>
       <c r="D5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F6A4C4-FB72-496F-85E7-64BAAB7F3D0A}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="5" max="5" width="27.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C6B9698-0386-4A1D-812D-465E61A63D79}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="8"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D379FC38-66D1-4621-AFF4-6204D5D4A4C1}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>21</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/ip_cimzes.xlsx
+++ b/ip_cimzes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vizsgaremek\NL_EZS_vizsga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NL_EZS_SP_vizsga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEDCD50-AABE-4318-A561-183480B29DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87474B8-5C07-49B7-828C-97F905B3517B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hálózatok" sheetId="1" r:id="rId1"/>
@@ -393,16 +393,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -416,10 +410,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -963,29 +958,29 @@
       <c r="A1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -993,16 +988,16 @@
       <c r="A3" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1010,16 +1005,16 @@
       <c r="A4" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1034,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C6B9698-0386-4A1D-812D-465E61A63D79}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -1045,104 +1040,85 @@
     <col min="6" max="6" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1163,82 +1139,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" t="s">
         <v>82</v>
       </c>
     </row>

--- a/ip_cimzes.xlsx
+++ b/ip_cimzes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NL_EZS_SP_vizsga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csabi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87474B8-5C07-49B7-828C-97F905B3517B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA1264D-9655-4BA2-ADD6-5F568D8E336E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3885" yWindow="3060" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hálózatok" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="176">
   <si>
     <t>Hálózat</t>
   </si>
@@ -65,9 +65,6 @@
     <t>10.10.20.0/24</t>
   </si>
   <si>
-    <t>10.10.30.0/24</t>
-  </si>
-  <si>
     <t>10.10.40.0/30</t>
   </si>
   <si>
@@ -273,13 +270,295 @@
   </si>
   <si>
     <t>10.10.30.129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPv6 prefix (SLAAC)	</t>
+  </si>
+  <si>
+    <t>2001:db8:abcd:10::/64</t>
+  </si>
+  <si>
+    <t>2001:db8:abcd:20::/64</t>
+  </si>
+  <si>
+    <t>2001:db8:abcd:30::/64</t>
+  </si>
+  <si>
+    <t>2001:db8:abcd:40::/64</t>
+  </si>
+  <si>
+    <t>Kapcsolat</t>
+  </si>
+  <si>
+    <t>IPv6 prefix</t>
+  </si>
+  <si>
+    <t>Eszköz A IPv6</t>
+  </si>
+  <si>
+    <t>Eszköz B IPv6</t>
+  </si>
+  <si>
+    <t>R1-Telephely ↔ Iroda3</t>
+  </si>
+  <si>
+    <t>2001:db8:4567:41::/127</t>
+  </si>
+  <si>
+    <t>2001:db8:4567:41::1/127</t>
+  </si>
+  <si>
+    <t>2001:db8:4567:41::2/127</t>
+  </si>
+  <si>
+    <t>R1-Telephely ↔ Iroda2</t>
+  </si>
+  <si>
+    <t>2001:db8:4567:40::/127</t>
+  </si>
+  <si>
+    <t>2001:db8:4567:40::1/127</t>
+  </si>
+  <si>
+    <t>2001:db8:4567:40::2/127</t>
+  </si>
+  <si>
+    <t>IPV6</t>
+  </si>
+  <si>
+    <t>Eszköz</t>
+  </si>
+  <si>
+    <t>IPv4 cím</t>
+  </si>
+  <si>
+    <t>IPv6 cím</t>
+  </si>
+  <si>
+    <t>R1-Telephely</t>
+  </si>
+  <si>
+    <t>–</t>
+  </si>
+  <si>
+    <t>2001:db8:2020::1/64</t>
+  </si>
+  <si>
+    <t>Win Server_Telephely</t>
+  </si>
+  <si>
+    <t>f0/2 (Switch 1)</t>
+  </si>
+  <si>
+    <t>10.10.20.2</t>
+  </si>
+  <si>
+    <t>2001:db8:2020:10::2/64</t>
+  </si>
+  <si>
+    <t>WRT300N Wifi Router</t>
+  </si>
+  <si>
+    <t>f0/1 (Switch 1)</t>
+  </si>
+  <si>
+    <t>10.10.20.3</t>
+  </si>
+  <si>
+    <t>2001:db8:2020:10::3/64</t>
+  </si>
+  <si>
+    <t>IT_PC</t>
+  </si>
+  <si>
+    <t>f0/24 (Switch 1)</t>
+  </si>
+  <si>
+    <t>10.10.20.4</t>
+  </si>
+  <si>
+    <t>2001:db8:2020:10::4/64</t>
+  </si>
+  <si>
+    <t>T_PC_01</t>
+  </si>
+  <si>
+    <t>f0/1 (Switch 2)</t>
+  </si>
+  <si>
+    <t>10.10.20.130</t>
+  </si>
+  <si>
+    <t>2001:db8:2020:20::1/64</t>
+  </si>
+  <si>
+    <t>T_PC_02</t>
+  </si>
+  <si>
+    <t>f0/2 (Switch 2)</t>
+  </si>
+  <si>
+    <t>10.10.20.131</t>
+  </si>
+  <si>
+    <t>2001:db8:2020:20::2/64</t>
+  </si>
+  <si>
+    <t>T_PC_03</t>
+  </si>
+  <si>
+    <t>f0/3 (Switch 2)</t>
+  </si>
+  <si>
+    <t>10.10.20.132</t>
+  </si>
+  <si>
+    <t>2001:db8:2020:20::3/64</t>
+  </si>
+  <si>
+    <t>T_Printer</t>
+  </si>
+  <si>
+    <t>f0/4 (Switch 2)</t>
+  </si>
+  <si>
+    <t>10.10.20.133</t>
+  </si>
+  <si>
+    <t>2001:db8:2020:20::4/64</t>
+  </si>
+  <si>
+    <t>T_PC_04</t>
+  </si>
+  <si>
+    <t>f0/5 (Switch 2)</t>
+  </si>
+  <si>
+    <t>10.10.20.134</t>
+  </si>
+  <si>
+    <t>2001:db8:2020:20::5/64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Példa cím: </t>
+  </si>
+  <si>
+    <t>2001:db8:abcd:10:1234:abcd:5678:90ef</t>
+  </si>
+  <si>
+    <t>Interface példanév</t>
+  </si>
+  <si>
+    <t>Gig0/0.20</t>
+  </si>
+  <si>
+    <t>2001:db8:abcd:20::1/64</t>
+  </si>
+  <si>
+    <t>Gig0/0.30</t>
+  </si>
+  <si>
+    <t>2001:db8:abcd:30::1/64</t>
+  </si>
+  <si>
+    <t>Gig0/0.40</t>
+  </si>
+  <si>
+    <t>2001:db8:abcd:40::1/64</t>
+  </si>
+  <si>
+    <t>Router-Iroda2</t>
+  </si>
+  <si>
+    <t>G0/0</t>
+  </si>
+  <si>
+    <t>2001:db8:3030::1/64</t>
+  </si>
+  <si>
+    <t>Iroda2_PC1</t>
+  </si>
+  <si>
+    <t>Switch1 f0/2</t>
+  </si>
+  <si>
+    <t>10.10.30.2</t>
+  </si>
+  <si>
+    <t>2001:db8:3030::2/64</t>
+  </si>
+  <si>
+    <t>Iroda2_PC2</t>
+  </si>
+  <si>
+    <t>Switch1 f0/3</t>
+  </si>
+  <si>
+    <t>10.10.30.3</t>
+  </si>
+  <si>
+    <t>2001:db8:3030::3/64</t>
+  </si>
+  <si>
+    <t>Iroda2_Printer</t>
+  </si>
+  <si>
+    <t>Switch1 f0/4</t>
+  </si>
+  <si>
+    <t>10.10.30.4</t>
+  </si>
+  <si>
+    <t>2001:db8:3030::4/64</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Switch2 f0/2</t>
+  </si>
+  <si>
+    <t>10.10.30.5</t>
+  </si>
+  <si>
+    <t>2001:db8:3030::5/64</t>
+  </si>
+  <si>
+    <t>WRT300N</t>
+  </si>
+  <si>
+    <t>Switch1 f0/1</t>
+  </si>
+  <si>
+    <t>10.10.30.6</t>
+  </si>
+  <si>
+    <t>2001:db8:3030::6/64</t>
+  </si>
+  <si>
+    <t>10.10.30.0/25</t>
+  </si>
+  <si>
+    <t>10.10.30.1 – 10.10.30.127</t>
+  </si>
+  <si>
+    <t>0.0.0.128</t>
+  </si>
+  <si>
+    <t>10.10.30.128/25</t>
+  </si>
+  <si>
+    <t>10.10.30.129-10.10.30.254</t>
+  </si>
+  <si>
+    <t>10.10.30.254</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,16 +574,60 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -389,11 +712,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -410,10 +744,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -720,8 +1079,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.28515625" customWidth="1"/>
@@ -732,7 +1091,7 @@
     <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,7 +1114,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -763,22 +1122,22 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
       <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -786,71 +1145,97 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F20" t="s">
-        <v>45</v>
+    <row r="15" spans="1:8" hidden="1"/>
+    <row r="21" spans="6:6">
+      <c r="F21" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -861,80 +1246,151 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>38</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E3" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>39</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E4" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>32</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="7">
+        <v>20</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="7">
+        <v>30</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="7">
+        <v>40</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -944,8 +1400,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F6A4C4-FB72-496F-85E7-64BAAB7F3D0A}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
     <col min="2" max="2" width="31.5703125" customWidth="1"/>
@@ -954,83 +1410,135 @@
     <col min="5" max="5" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="13"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="6" t="s">
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="7"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21">
+      <c r="B8" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C6B9698-0386-4A1D-812D-465E61A63D79}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
@@ -1040,95 +1548,278 @@
     <col min="6" max="6" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>64</v>
       </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="26.25">
+      <c r="A8" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="11"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="25.5">
+      <c r="A10" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="25.5">
+      <c r="A11" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="7">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25.5">
+      <c r="A12" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="7">
+        <v>10</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="25.5">
+      <c r="A13" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="7">
+        <v>10</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="25.5">
+      <c r="A14" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="7">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D14" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="25.5">
+      <c r="A15" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="7">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" t="s">
-        <v>72</v>
+      <c r="D15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="25.5">
+      <c r="A16" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="7">
+        <v>20</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="25.5">
+      <c r="A17" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="7">
+        <v>20</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="25.5">
+      <c r="A18" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="7">
+        <v>20</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A8:E8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D379FC38-66D1-4621-AFF4-6204D5D4A4C1}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
@@ -1138,87 +1829,196 @@
     <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>77</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
         <v>78</v>
       </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>79</v>
       </c>
-      <c r="E3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>80</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" t="s">
         <v>81</v>
       </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" t="s">
-        <v>82</v>
+    </row>
+    <row r="9" spans="1:6" ht="28.5">
+      <c r="A9" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="25.5">
+      <c r="A11" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25.5">
+      <c r="A12" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="25.5">
+      <c r="A13" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="25.5">
+      <c r="A14" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="25.5">
+      <c r="A15" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="25.5">
+      <c r="A16" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:D9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ip_cimzes.xlsx
+++ b/ip_cimzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\NL_EZS_SP_vizsga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC00CDD-A373-4634-BC9D-F5D813E7395E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FD3C89-BFA2-4A78-B2EA-98BE0C070726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="1740" windowWidth="21600" windowHeight="11700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="2085" windowWidth="21600" windowHeight="11700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hálózatok" sheetId="1" r:id="rId1"/>
@@ -957,10 +957,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2724,12 +2720,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="cd81826e-3218-48a1-acf5-dea1d0e4e8c6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2974,17 +2969,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="cd81826e-3218-48a1-acf5-dea1d0e4e8c6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C3793F4-448F-4A19-8064-02A85813F285}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61BD3DFA-441F-4125-9475-6E9B4E6B9FA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="130ea38e-f73c-4753-a73c-94b2bd1348bc"/>
+    <ds:schemaRef ds:uri="cd81826e-3218-48a1-acf5-dea1d0e4e8c6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3009,18 +3014,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61BD3DFA-441F-4125-9475-6E9B4E6B9FA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C3793F4-448F-4A19-8064-02A85813F285}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="130ea38e-f73c-4753-a73c-94b2bd1348bc"/>
-    <ds:schemaRef ds:uri="cd81826e-3218-48a1-acf5-dea1d0e4e8c6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>